--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575864749</v>
+        <v>46157.93121008739</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121008739</v>
+        <v>46157.93186664781</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186664781</v>
+        <v>46157.93407218099</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407218099</v>
+        <v>46157.93725371528</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725371528</v>
+        <v>46158.2822284809</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2822284809</v>
+        <v>46158.29711808739</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29711808739</v>
+        <v>46158.2982293665</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2982293665</v>
+        <v>46158.33393849459</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393849459</v>
+        <v>46158.36863597588</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Пушкарь- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863597588</v>
+        <v>46158.37294606354</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
